--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -441,32 +441,32 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>crossreference</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>examples</t>
         </is>
       </c>
     </row>
@@ -521,13 +521,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,21 +538,21 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>temporal region</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -560,16 +560,11 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -577,7 +572,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -586,14 +581,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:008525</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -602,7 +600,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>intervention contact event duration</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -610,236 +608,239 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
+          <t>An &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 1 hour; 30 minutes; 2 minutes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:008700</t>
+          <t>BCIO:008575</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>interval between intervention temporal parts</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
+          <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>How often intervention sessions or digital contacts are planned to occur</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>The planned duration of a break between two parts of an intervention</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "2 weeks"; "1 day"</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; twice a week; daily; one a week</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050904</t>
+          <t>BCIO:008565</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>intervention contact event number statistic</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>The planned duration of a part of an intervention</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 weeks</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050912</t>
+          <t>BCIO:008560</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>intervention duration</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>mean intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The planned duration of an intervention</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 months; 1 year</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050497</t>
+          <t>BCIO:008530</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>temporal reference associated with the intervention</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>median intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>A &lt;temporal region&gt; against which an intervention temporal part is referenced.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
+We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050907</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>maximum intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050502</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>minimum intervention contact event number</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050903</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>intervention contact event frequency statistic</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050500</t>
+          <t>BCIO:051010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -847,30 +848,26 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>minimum intervention contact event frequency</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>intervention attribute</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
+          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050496</t>
+          <t>BCIO:008580</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -881,27 +878,31 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>median intervention contact event frequency</t>
+          <t>order of intervention temporal parts</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "After questionnaires were completed, feedback was selected
+out of a database with messages for each possible combination
+of answers."; "The PA advice started with a general introduction,
+followed by normative feedback, which related students’ PA
+levels to the PA guidelines."</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050906</t>
+          <t>BCIO:009000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -912,27 +913,27 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>maximum intervention contact event frequency</t>
+          <t>intervention schedule of delivery</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>An intervention attribute that is its temporal organisation.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Includes the start and end of the BCI and its parts.</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050911</t>
+          <t>BCIO:008540</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -941,29 +942,34 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>mean intervention contact event frequency</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>irregular intervention schedule</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:008710</t>
+          <t>BCIO:008535</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -971,103 +977,83 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>intervention temporal part frequency</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>regular intervention schedule</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
+          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>How often intervention parts are planned to occur</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly. 
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Participants took part in 90 minutes of PA "weekly"</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:008515</t>
+          <t>COB:0000082</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>number of intervention contact events</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; one; 6; 12; twenty</t>
+          <t>A process that is initiated by an agent who intends to carry out a plan to achieve an objective through one or more actions as described in a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050516</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>A planned process that has the aim of influencing an outcome.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050518</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1075,61 +1061,63 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>mean intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050517</t>
+          <t>BCIO:008505</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>intervention temporal part</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>maximum intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>A planned part of an intervention</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050519</t>
+          <t>BCIO:008510</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1137,216 +1125,178 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>median intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>intervention contact event</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A counselling session; An online chat session; An advertisement display.</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050520</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>minimum intervention temporal part frequency statistic</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050506</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>intervention temporal part duration statistic</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050512</t>
+          <t>PATO:0000044</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>median intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
+          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:050508</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>maximum intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050514</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>minimum intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050510</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>mean intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+          <t>An information content entity that is intended to be one or more truthful statement(s) about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050905</t>
+          <t>BCIO:050903</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1356,28 +1306,28 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>intervention duration statistic</t>
+          <t>intervention contact event frequency statistic</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050501</t>
+          <t>BCIO:050911</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1388,27 +1338,27 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>minimum intervention duration</t>
+          <t>mean intervention contact event frequency</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the average value calculated from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050908</t>
+          <t>BCIO:050496</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1419,27 +1369,27 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>maximum intervention duration</t>
+          <t>median intervention contact event frequency</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the central value of a collection of  intervention contact event frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050909</t>
+          <t>BCIO:050500</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1450,27 +1400,27 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>mean intervention duration</t>
+          <t>minimum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the lowest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:050498</t>
+          <t>BCIO:050906</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1481,27 +1431,27 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>median intervention duration</t>
+          <t>maximum intervention contact event frequency</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>An &lt;intervention contact event frequency statistic&gt; that is the highest value from a collection of intervention contact event frequencies.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:050504</t>
+          <t>BCIO:008710</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1511,28 +1461,34 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>total intervention contact event duration</t>
+          <t>intervention temporal part frequency</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about the amount of time that the participant is exposed to the intervention through its contact events.</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is how often intervention temporal parts occur within an intervention.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>How often intervention parts are planned to occur</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>This is useful when grouping contact events together to the schedule of an intervention. For example, authors may describe participants as taking part in 90 minutes of physical activity weekly. These 90 minutes could be split across several contact events, however together these contact events form an intervention part which occurs weekly. 
+This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Participants took part in 90 minutes of PA "weekly"</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 150 minutes; 12 hours</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:050910</t>
+          <t>BCIO:050506</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1540,30 +1496,30 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>maximum total intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>intervention temporal part duration statistic</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the highest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050495</t>
+          <t>BCIO:050512</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1574,27 +1530,27 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>mean total intervention contact event duration</t>
+          <t>median intervention temporal part duration</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the average value calculated from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the central value of a collection of intervention temporal part durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050499</t>
+          <t>BCIO:050514</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1605,27 +1561,27 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>median total intervention contact event duration</t>
+          <t>minimum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the lowest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050503</t>
+          <t>BCIO:050508</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1636,27 +1592,27 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>minimum total intervention contact event duration</t>
+          <t>maximum intervention temporal part duration</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A &lt;total intervention contact event duration&gt; that is the lowest value from a collection of total contact event durations.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that denotes the highest value from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050505</t>
+          <t>BCIO:050510</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1664,30 +1620,30 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>intervention contact event duration statistic</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mean intervention temporal part duration</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>An &lt;intervention temporal part duration statistic&gt; that is the average value calculated from a collection of intervention temporal part durations.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050507</t>
+          <t>BCIO:050516</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1695,30 +1651,30 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>maximum intervention contact event duration</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>intervention temporal part frequency statistic</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050511</t>
+          <t>BCIO:050519</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1729,27 +1685,27 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>median intervention contact event duration</t>
+          <t>median intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the central value of a collection of intervention temporal part frequencies when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050509</t>
+          <t>BCIO:050518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1760,27 +1716,27 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>mean intervention contact event duration</t>
+          <t>mean intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the average value calculated from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050513</t>
+          <t>BCIO:050517</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1791,174 +1747,218 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>minimum intervention contact event duration</t>
+          <t>maximum intervention temporal part frequency statistic</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the highest value from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:050520</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>minimum intervention temporal part frequency statistic</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
-        </is>
-      </c>
+          <t>An &lt;intervention temporal part frequency statistic&gt; that is the lowest value from a collection of intervention temporal part frequencies.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PATO:0000044</t>
+          <t>BCIO:008700</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>frequency</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>intervention contact event frequency</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of the number of the bearer's repetitive actions in a particular time.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>A &lt;data item&gt; about the number times an intervention contact event occurs per unit of time.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>How often intervention sessions or digital contacts are planned to occur</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; twice a week; daily; one a week</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:050905</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>intervention duration statistic</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>A &lt;data item&gt; that is about a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:050498</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>median intervention duration</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
-        </is>
-      </c>
+          <t>An &lt;intervention duration statistic&gt; that is the central value of a collection of intervention durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:050909</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>mean intervention duration</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
+          <t>An &lt;intervention duration statistic&gt; that is the average value calculated from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:037000</t>
+          <t>BCIO:050501</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>intervention</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>minimum intervention duration</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
-        </is>
-      </c>
+          <t>An &lt;intervention duration statistic&gt; that is the lowest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:003000</t>
+          <t>BCIO:050908</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1966,63 +1966,61 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>behaviour change intervention</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>maximum intervention duration</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>An &lt;intervention duration statistic&gt; that is the highest value from a collection of intervention durations.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:008505</t>
+          <t>BCIO:050904</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>intervention temporal part</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>intervention contact event number statistic</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A &lt;planned process&gt; that is a part of an intervention.</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>A planned part of an intervention</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Temporal parts are defined by the authors of reports. They usually group contact events with similar delivery (e.g. face-to-face), content (e.g. CBT), or contextual features (e.g. school lessons), in order to describe their schedule. 
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; counselling sessions; the first 6 weeks of the intervention; group discussion; a presentation; the last 4 weeks of the intervention</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:008510</t>
+          <t>BCIO:050907</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2030,79 +2028,92 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>intervention contact event</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event number</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>An &lt;intervention temporal part&gt; that is an occasion in which a member of an intervention population comes into contact with an intervention.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the highest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>All contact events are temporal parts, but not all temporal parts are contact events. Whilst contact events are single continuous events, temporal parts of an intervention can  group together multiple different contact events which might have similar features. For example, a set of 10 counselling sessions might be a temporal part within an intervention. The same intervention can have a set of 5 exercise sessions. These 5 sessions together make up another temporal part. Each single session within these parts  is a contact event.
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A counselling session; An online chat session; An advertisement display.</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:050912</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>mean intervention contact event number</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>An &lt;intervention contact event number statistic&gt; that is the average value calculated from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:050502</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>minimum intervention contact event number</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>An &lt;intervention contact event number statistic&gt; that is the lowest value from a collection of intervention contact event numbers.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:051010</t>
+          <t>BCIO:050497</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2110,26 +2121,30 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>intervention attribute</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>median intervention contact event number</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A &lt;process attribute&gt; whose bearer is an intervention.</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>An &lt;intervention contact event number statistic&gt; that is the central value of a collection of  intervention contact event numbers when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:009000</t>
+          <t>BCIO:050504</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2137,30 +2152,35 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>intervention schedule of delivery</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>total intervention contact event duration</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>An intervention attribute that is its temporal organisation.</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about the amount of time that the participant is exposed to the intervention through its contact events.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>The planned total duration of all sessions or digital contacts in an intervention or part.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 150 minutes; 12 hours</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; Includes the start and end of the BCI and its parts.</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:008540</t>
+          <t>BCIO:050495</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2169,34 +2189,29 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>irregular intervention schedule</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>mean total intervention contact event duration</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of contact events change over the course of a temporal part or intervention.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts vary across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the average value calculated from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; telephone feedback sessions were more frequent during the first 6 weeks; participants were free to access the app whenever they desired</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:008535</t>
+          <t>BCIO:050503</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2205,34 +2220,29 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>regular intervention schedule</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>minimum total intervention contact event duration</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>An &lt;intervention schedule of delivery&gt; in which the frequency and duration of Intervention temporal parts are uniform across the course of an intervention or intervention part.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>A type of schedule which plans that the duration and frequency of sessions or digital contacts remain constant across the course of an intervention</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the lowest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; the length and regularity of sessions were consistent across the duration of the intervention, taking place for an hour each week</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:008580</t>
+          <t>BCIO:050910</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2243,249 +2253,244 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>order of intervention temporal parts</t>
+          <t>maximum total intervention contact event duration</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>An &lt;intervention attribute&gt; that is the  temporal positioning of intervention temporal parts.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>A &lt;total intervention contact event duration&gt; that is the highest value from a collection of total contact event durations.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "After questionnaires were completed, feedback was selected
-out of a database with messages for each possible combination
-of answers."; "The PA advice started with a general introduction,
-followed by normative feedback, which related students’ PA
-levels to the PA guidelines."</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:050499</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>median total intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A &lt;total intervention contact event duration&gt; that is the central value of a collection of total contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:008530</t>
+          <t>BCIO:050505</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>temporal reference associated with the intervention</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>intervention contact event duration statistic</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A &lt;temporal region&gt; against which an intervention temporal part is referenced.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>A statement which describes how the delivery of intervention parts is scheduled relative to associated external events.</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is about a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Temporal references are used by authors when there is a behaviourally relevant event which structures the schedule of a BCI. This can include things like quit dates, childbirth, medical operations etc.
-We often refer to timepoints when we mean a specific time or some extended period (e.g., Monday). This class allows for the natural usage of a term while maintaining ontological coherence.
-This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; A feedback call was scheduled to be delivered around 6 months after the birth of the baby; The smoking intervention started 2 weeks after participants were enrolled into an inpatient setting</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050507</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>maximum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the highest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:008575</t>
+          <t>BCIO:050513</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>interval between intervention temporal parts</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>minimum intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the end of one intervention temporal part and the beginning of a subsequent intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>The planned duration of a break between two parts of an intervention</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the lowest value from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; "2 weeks"; "1 day"</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:008565</t>
+          <t>BCIO:050511</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>intervention temporal part duration</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>median intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention temporal part.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>The planned duration of a part of an intervention</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the central value of a collection of intervention contact event durations when they are arranged in ascending order.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 weeks</t>
-        </is>
-      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:008560</t>
+          <t>BCIO:050509</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>intervention duration</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>mean intervention contact event duration</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A &lt;temporal interval&gt; between the start and end of an intervention.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>The planned duration of an intervention</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>An &lt;intervention contact event duration statistic&gt; that is the average value calculated from a collection of intervention contact event durations.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 6 weeks; 2 months; 1 year</t>
-        </is>
-      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:008525</t>
+          <t>BCIO:008515</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>intervention contact event duration</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>number of intervention contact events</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>An &lt;temporal interval&gt; between the start and end of an intervention contact event.</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>A &lt;data item&gt; that is the number of contact events in an intervention temporal part.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>The planned total number of sessions or digital contacts in an intervention or part</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; one; 6; 12; twenty</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>This class was previously specific to behaviour change interventions, but was expanded to be relevant to other types of interventions, allowing it to be applied more broadly. It can still be used for behaviour change interventions in the same way as before.; 1 hour; 30 minutes; 2 minutes</t>
-        </is>
-      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
